--- a/artfynd/A 42064-2024 artfynd.xlsx
+++ b/artfynd/A 42064-2024 artfynd.xlsx
@@ -2970,10 +2970,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120922589</v>
+        <v>120922501</v>
       </c>
       <c r="B22" t="n">
-        <v>78598</v>
+        <v>91031</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2982,25 +2982,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582049</v>
+        <v>581743</v>
       </c>
       <c r="R22" t="n">
-        <v>7193913</v>
+        <v>7194427</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3066,6 +3066,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3082,10 +3097,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120922501</v>
+        <v>120922589</v>
       </c>
       <c r="B23" t="n">
-        <v>91031</v>
+        <v>78598</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3094,25 +3109,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3122,10 +3137,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581743</v>
+        <v>582049</v>
       </c>
       <c r="R23" t="n">
-        <v>7194427</v>
+        <v>7193913</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3157,7 +3172,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3167,7 +3182,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3178,21 +3193,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3321,10 +3321,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120922481</v>
+        <v>120922500</v>
       </c>
       <c r="B25" t="n">
-        <v>57348</v>
+        <v>90683</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3337,39 +3337,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582249</v>
+        <v>581739</v>
       </c>
       <c r="R25" t="n">
-        <v>7194088</v>
+        <v>7194428</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3401,7 +3396,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3411,7 +3406,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3438,10 +3433,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120922500</v>
+        <v>120922481</v>
       </c>
       <c r="B26" t="n">
-        <v>90683</v>
+        <v>57348</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3454,34 +3449,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581739</v>
+        <v>582249</v>
       </c>
       <c r="R26" t="n">
-        <v>7194428</v>
+        <v>7194088</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3886,10 +3886,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120922587</v>
+        <v>120922487</v>
       </c>
       <c r="B30" t="n">
-        <v>77982</v>
+        <v>57348</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3902,34 +3902,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>582037</v>
+        <v>582033</v>
       </c>
       <c r="R30" t="n">
-        <v>7193934</v>
+        <v>7194312</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3961,7 +3966,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3971,7 +3976,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3998,10 +4003,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120922487</v>
+        <v>120922482</v>
       </c>
       <c r="B31" t="n">
-        <v>57348</v>
+        <v>57501</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4014,27 +4019,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4043,10 +4047,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>582033</v>
+        <v>582136</v>
       </c>
       <c r="R31" t="n">
-        <v>7194312</v>
+        <v>7194281</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4078,7 +4082,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4088,7 +4092,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4115,10 +4119,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120922482</v>
+        <v>120922587</v>
       </c>
       <c r="B32" t="n">
-        <v>57501</v>
+        <v>77982</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4131,38 +4135,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>6437</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>582136</v>
+        <v>582037</v>
       </c>
       <c r="R32" t="n">
-        <v>7194281</v>
+        <v>7193934</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4343,10 +4343,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120922488</v>
+        <v>120922590</v>
       </c>
       <c r="B34" t="n">
-        <v>57348</v>
+        <v>78598</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4359,39 +4359,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581950</v>
+        <v>582118</v>
       </c>
       <c r="R34" t="n">
-        <v>7194247</v>
+        <v>7193927</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4423,7 +4418,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4433,7 +4428,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4460,10 +4455,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120922590</v>
+        <v>120922488</v>
       </c>
       <c r="B35" t="n">
-        <v>78598</v>
+        <v>57348</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4476,34 +4471,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>582118</v>
+        <v>581950</v>
       </c>
       <c r="R35" t="n">
-        <v>7193927</v>
+        <v>7194247</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 42064-2024 artfynd.xlsx
+++ b/artfynd/A 42064-2024 artfynd.xlsx
@@ -2858,10 +2858,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120922510</v>
+        <v>120922513</v>
       </c>
       <c r="B21" t="n">
-        <v>78598</v>
+        <v>74708</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2874,21 +2874,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2898,10 +2898,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581763</v>
+        <v>581664</v>
       </c>
       <c r="R21" t="n">
-        <v>7194446</v>
+        <v>7194719</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2970,10 +2970,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120922501</v>
+        <v>120922487</v>
       </c>
       <c r="B22" t="n">
-        <v>91031</v>
+        <v>57351</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2982,38 +2982,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581743</v>
+        <v>582033</v>
       </c>
       <c r="R22" t="n">
-        <v>7194427</v>
+        <v>7194312</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3045,7 +3050,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3055,7 +3060,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3066,21 +3071,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3097,10 +3087,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120922589</v>
+        <v>120922585</v>
       </c>
       <c r="B23" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3137,10 +3127,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582049</v>
+        <v>581987</v>
       </c>
       <c r="R23" t="n">
-        <v>7193913</v>
+        <v>7193934</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3172,7 +3162,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3182,7 +3172,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3209,10 +3199,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120922588</v>
+        <v>120922590</v>
       </c>
       <c r="B24" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3249,10 +3239,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582037</v>
+        <v>582118</v>
       </c>
       <c r="R24" t="n">
-        <v>7193934</v>
+        <v>7193927</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3284,7 +3274,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3294,7 +3284,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3321,10 +3311,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120922500</v>
+        <v>120922481</v>
       </c>
       <c r="B25" t="n">
-        <v>90683</v>
+        <v>57351</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3337,34 +3327,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581739</v>
+        <v>582249</v>
       </c>
       <c r="R25" t="n">
-        <v>7194428</v>
+        <v>7194088</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3396,7 +3391,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3406,7 +3401,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3433,10 +3428,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120922481</v>
+        <v>120922507</v>
       </c>
       <c r="B26" t="n">
-        <v>57348</v>
+        <v>90693</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3449,39 +3444,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582249</v>
+        <v>581739</v>
       </c>
       <c r="R26" t="n">
-        <v>7194088</v>
+        <v>7194433</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3513,7 +3503,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3523,7 +3513,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3550,10 +3540,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120922584</v>
+        <v>120922486</v>
       </c>
       <c r="B27" t="n">
-        <v>79680</v>
+        <v>78601</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3566,21 +3556,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3590,10 +3580,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581988</v>
+        <v>582067</v>
       </c>
       <c r="R27" t="n">
-        <v>7193931</v>
+        <v>7194258</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3625,7 +3615,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3635,7 +3625,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3662,10 +3652,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120922504</v>
+        <v>120922482</v>
       </c>
       <c r="B28" t="n">
-        <v>90687</v>
+        <v>57504</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3678,34 +3668,38 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581741</v>
+        <v>582136</v>
       </c>
       <c r="R28" t="n">
-        <v>7194431</v>
+        <v>7194281</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3737,7 +3731,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3747,7 +3741,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3774,10 +3768,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120922591</v>
+        <v>120922586</v>
       </c>
       <c r="B29" t="n">
-        <v>78598</v>
+        <v>80558</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3790,21 +3784,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3814,10 +3808,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>582228</v>
+        <v>582040</v>
       </c>
       <c r="R29" t="n">
-        <v>7193932</v>
+        <v>7193935</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3849,7 +3843,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3859,7 +3853,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3886,10 +3880,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120922487</v>
+        <v>120922484</v>
       </c>
       <c r="B30" t="n">
-        <v>57348</v>
+        <v>79642</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3898,43 +3892,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>582033</v>
+        <v>582070</v>
       </c>
       <c r="R30" t="n">
-        <v>7194312</v>
+        <v>7194257</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3966,7 +3955,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3976,7 +3965,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4003,10 +3992,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120922482</v>
+        <v>120922503</v>
       </c>
       <c r="B31" t="n">
-        <v>57501</v>
+        <v>91090</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4019,38 +4008,29 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>582136</v>
+        <v>581741</v>
       </c>
       <c r="R31" t="n">
-        <v>7194281</v>
+        <v>7194429</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4082,7 +4062,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4092,7 +4072,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4119,10 +4099,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120922587</v>
+        <v>120922504</v>
       </c>
       <c r="B32" t="n">
-        <v>77982</v>
+        <v>90697</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4135,21 +4115,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4159,10 +4139,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>582037</v>
+        <v>581741</v>
       </c>
       <c r="R32" t="n">
-        <v>7193934</v>
+        <v>7194431</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4194,7 +4174,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4204,7 +4184,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4231,10 +4211,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120922507</v>
+        <v>120922512</v>
       </c>
       <c r="B33" t="n">
-        <v>90683</v>
+        <v>78601</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4247,21 +4227,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4271,10 +4251,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581739</v>
+        <v>581763</v>
       </c>
       <c r="R33" t="n">
-        <v>7194433</v>
+        <v>7194521</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4306,7 +4286,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4316,7 +4296,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4343,10 +4323,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120922590</v>
+        <v>120922485</v>
       </c>
       <c r="B34" t="n">
-        <v>78598</v>
+        <v>79718</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4355,25 +4335,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4383,10 +4363,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>582118</v>
+        <v>582071</v>
       </c>
       <c r="R34" t="n">
-        <v>7193927</v>
+        <v>7194257</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4418,7 +4398,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4428,7 +4408,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4455,10 +4435,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120922488</v>
+        <v>120922587</v>
       </c>
       <c r="B35" t="n">
-        <v>57348</v>
+        <v>77985</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4471,39 +4451,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>581950</v>
+        <v>582037</v>
       </c>
       <c r="R35" t="n">
-        <v>7194247</v>
+        <v>7193934</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4535,7 +4510,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4545,7 +4520,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4572,10 +4547,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120922586</v>
+        <v>120922588</v>
       </c>
       <c r="B36" t="n">
-        <v>80555</v>
+        <v>78601</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4588,21 +4563,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4612,10 +4587,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>582040</v>
+        <v>582037</v>
       </c>
       <c r="R36" t="n">
-        <v>7193935</v>
+        <v>7193934</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4684,10 +4659,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120922512</v>
+        <v>120922488</v>
       </c>
       <c r="B37" t="n">
-        <v>78598</v>
+        <v>57351</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4700,34 +4675,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581763</v>
+        <v>581950</v>
       </c>
       <c r="R37" t="n">
-        <v>7194521</v>
+        <v>7194247</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4759,7 +4739,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4769,7 +4749,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4796,10 +4776,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120922515</v>
+        <v>120922501</v>
       </c>
       <c r="B38" t="n">
-        <v>78598</v>
+        <v>91041</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4808,25 +4788,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4836,10 +4816,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581662</v>
+        <v>581743</v>
       </c>
       <c r="R38" t="n">
-        <v>7194722</v>
+        <v>7194427</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4871,7 +4851,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4881,7 +4861,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4892,6 +4872,21 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4908,10 +4903,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120922503</v>
+        <v>120922502</v>
       </c>
       <c r="B39" t="n">
-        <v>91080</v>
+        <v>90983</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4924,16 +4919,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6040186</v>
+        <v>658</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581741</v>
+        <v>581743</v>
       </c>
       <c r="R39" t="n">
-        <v>7194429</v>
+        <v>7194428</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5015,10 +5015,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120922483</v>
+        <v>120922515</v>
       </c>
       <c r="B40" t="n">
-        <v>79680</v>
+        <v>78601</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5031,21 +5031,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5055,10 +5055,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>582070</v>
+        <v>581662</v>
       </c>
       <c r="R40" t="n">
-        <v>7194255</v>
+        <v>7194722</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5130,7 +5130,7 @@
         <v>120922489</v>
       </c>
       <c r="B41" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5239,10 +5239,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120922508</v>
+        <v>120922483</v>
       </c>
       <c r="B42" t="n">
-        <v>78598</v>
+        <v>79683</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5255,21 +5255,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581736</v>
+        <v>582070</v>
       </c>
       <c r="R42" t="n">
-        <v>7194434</v>
+        <v>7194255</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5351,10 +5351,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120922484</v>
+        <v>120922508</v>
       </c>
       <c r="B43" t="n">
-        <v>79639</v>
+        <v>78601</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5363,25 +5363,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5391,10 +5391,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>582070</v>
+        <v>581736</v>
       </c>
       <c r="R43" t="n">
-        <v>7194257</v>
+        <v>7194434</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5463,10 +5463,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120922513</v>
+        <v>120922500</v>
       </c>
       <c r="B44" t="n">
-        <v>74705</v>
+        <v>90693</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5479,21 +5479,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5503,10 +5503,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581664</v>
+        <v>581739</v>
       </c>
       <c r="R44" t="n">
-        <v>7194719</v>
+        <v>7194428</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5575,10 +5575,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120922585</v>
+        <v>120922591</v>
       </c>
       <c r="B45" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5615,10 +5615,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581987</v>
+        <v>582228</v>
       </c>
       <c r="R45" t="n">
-        <v>7193934</v>
+        <v>7193932</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5650,7 +5650,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5687,10 +5687,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120922486</v>
+        <v>120922584</v>
       </c>
       <c r="B46" t="n">
-        <v>78598</v>
+        <v>79683</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5703,21 +5703,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5727,10 +5727,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>582067</v>
+        <v>581988</v>
       </c>
       <c r="R46" t="n">
-        <v>7194258</v>
+        <v>7193931</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5799,10 +5799,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120922485</v>
+        <v>120922510</v>
       </c>
       <c r="B47" t="n">
-        <v>79715</v>
+        <v>78601</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5811,25 +5811,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5839,10 +5839,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>582071</v>
+        <v>581763</v>
       </c>
       <c r="R47" t="n">
-        <v>7194257</v>
+        <v>7194446</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5911,10 +5911,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120922502</v>
+        <v>120922589</v>
       </c>
       <c r="B48" t="n">
-        <v>90973</v>
+        <v>78601</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5927,21 +5927,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5951,10 +5951,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581743</v>
+        <v>582049</v>
       </c>
       <c r="R48" t="n">
-        <v>7194428</v>
+        <v>7193913</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5986,7 +5986,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 42064-2024 artfynd.xlsx
+++ b/artfynd/A 42064-2024 artfynd.xlsx
@@ -4211,10 +4211,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120922512</v>
+        <v>120922485</v>
       </c>
       <c r="B33" t="n">
-        <v>78601</v>
+        <v>79718</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4223,25 +4223,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4251,10 +4251,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581763</v>
+        <v>582071</v>
       </c>
       <c r="R33" t="n">
-        <v>7194521</v>
+        <v>7194257</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4286,7 +4286,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4323,10 +4323,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120922485</v>
+        <v>120922512</v>
       </c>
       <c r="B34" t="n">
-        <v>79718</v>
+        <v>78601</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4335,25 +4335,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4363,10 +4363,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>582071</v>
+        <v>581763</v>
       </c>
       <c r="R34" t="n">
-        <v>7194257</v>
+        <v>7194521</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4659,10 +4659,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120922488</v>
+        <v>120922501</v>
       </c>
       <c r="B37" t="n">
-        <v>57351</v>
+        <v>91041</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4671,43 +4671,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581950</v>
+        <v>581743</v>
       </c>
       <c r="R37" t="n">
-        <v>7194247</v>
+        <v>7194427</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4739,7 +4734,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4749,7 +4744,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4760,6 +4755,21 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4776,10 +4786,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120922501</v>
+        <v>120922488</v>
       </c>
       <c r="B38" t="n">
-        <v>91041</v>
+        <v>57351</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4788,38 +4798,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581743</v>
+        <v>581950</v>
       </c>
       <c r="R38" t="n">
-        <v>7194427</v>
+        <v>7194247</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4851,7 +4866,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4861,7 +4876,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4872,21 +4887,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5463,10 +5463,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120922500</v>
+        <v>120922591</v>
       </c>
       <c r="B44" t="n">
-        <v>90693</v>
+        <v>78601</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5479,21 +5479,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5503,10 +5503,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581739</v>
+        <v>582228</v>
       </c>
       <c r="R44" t="n">
-        <v>7194428</v>
+        <v>7193932</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5575,10 +5575,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120922591</v>
+        <v>120922500</v>
       </c>
       <c r="B45" t="n">
-        <v>78601</v>
+        <v>90693</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5591,21 +5591,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5615,10 +5615,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>582228</v>
+        <v>581739</v>
       </c>
       <c r="R45" t="n">
-        <v>7193932</v>
+        <v>7194428</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5650,7 +5650,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 42064-2024 artfynd.xlsx
+++ b/artfynd/A 42064-2024 artfynd.xlsx
@@ -3199,10 +3199,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120922590</v>
+        <v>120922481</v>
       </c>
       <c r="B24" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3215,34 +3215,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582118</v>
+        <v>582249</v>
       </c>
       <c r="R24" t="n">
-        <v>7193927</v>
+        <v>7194088</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3274,7 +3279,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3284,7 +3289,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3311,10 +3316,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120922481</v>
+        <v>120922590</v>
       </c>
       <c r="B25" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3327,39 +3332,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582249</v>
+        <v>582118</v>
       </c>
       <c r="R25" t="n">
-        <v>7194088</v>
+        <v>7193927</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4659,10 +4659,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120922501</v>
+        <v>120922488</v>
       </c>
       <c r="B37" t="n">
-        <v>91041</v>
+        <v>57351</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4671,38 +4671,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581743</v>
+        <v>581950</v>
       </c>
       <c r="R37" t="n">
-        <v>7194427</v>
+        <v>7194247</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4734,7 +4739,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4744,7 +4749,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4755,21 +4760,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4786,10 +4776,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120922488</v>
+        <v>120922501</v>
       </c>
       <c r="B38" t="n">
-        <v>57351</v>
+        <v>91041</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4798,43 +4788,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581950</v>
+        <v>581743</v>
       </c>
       <c r="R38" t="n">
-        <v>7194247</v>
+        <v>7194427</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4866,7 +4851,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4876,7 +4861,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4887,6 +4872,21 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5463,10 +5463,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120922591</v>
+        <v>120922500</v>
       </c>
       <c r="B44" t="n">
-        <v>78601</v>
+        <v>90693</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5479,21 +5479,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5503,10 +5503,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>582228</v>
+        <v>581739</v>
       </c>
       <c r="R44" t="n">
-        <v>7193932</v>
+        <v>7194428</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5575,10 +5575,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120922500</v>
+        <v>120922591</v>
       </c>
       <c r="B45" t="n">
-        <v>90693</v>
+        <v>78601</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5591,21 +5591,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5615,10 +5615,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581739</v>
+        <v>582228</v>
       </c>
       <c r="R45" t="n">
-        <v>7194428</v>
+        <v>7193932</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5650,7 +5650,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 42064-2024 artfynd.xlsx
+++ b/artfynd/A 42064-2024 artfynd.xlsx
@@ -2858,10 +2858,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120922513</v>
+        <v>120922503</v>
       </c>
       <c r="B21" t="n">
-        <v>74708</v>
+        <v>91090</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2874,21 +2874,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2898,10 +2893,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581664</v>
+        <v>581741</v>
       </c>
       <c r="R21" t="n">
-        <v>7194719</v>
+        <v>7194429</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2933,7 +2928,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2943,7 +2938,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2970,10 +2965,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120922487</v>
+        <v>120922507</v>
       </c>
       <c r="B22" t="n">
-        <v>57351</v>
+        <v>90693</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2986,39 +2981,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582033</v>
+        <v>581739</v>
       </c>
       <c r="R22" t="n">
-        <v>7194312</v>
+        <v>7194433</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3050,7 +3040,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3060,7 +3050,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3087,7 +3077,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120922585</v>
+        <v>120922508</v>
       </c>
       <c r="B23" t="n">
         <v>78601</v>
@@ -3127,10 +3117,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581987</v>
+        <v>581736</v>
       </c>
       <c r="R23" t="n">
-        <v>7193934</v>
+        <v>7194434</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3162,7 +3152,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3172,7 +3162,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3199,10 +3189,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120922481</v>
+        <v>120922500</v>
       </c>
       <c r="B24" t="n">
-        <v>57351</v>
+        <v>90693</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3215,39 +3205,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582249</v>
+        <v>581739</v>
       </c>
       <c r="R24" t="n">
-        <v>7194088</v>
+        <v>7194428</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3279,7 +3264,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3289,7 +3274,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3316,10 +3301,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120922590</v>
+        <v>120922482</v>
       </c>
       <c r="B25" t="n">
-        <v>78601</v>
+        <v>57504</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3332,34 +3317,38 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582118</v>
+        <v>582136</v>
       </c>
       <c r="R25" t="n">
-        <v>7193927</v>
+        <v>7194281</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3391,7 +3380,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3401,7 +3390,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3428,10 +3417,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120922507</v>
+        <v>120922585</v>
       </c>
       <c r="B26" t="n">
-        <v>90693</v>
+        <v>78601</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3444,21 +3433,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3468,10 +3457,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581739</v>
+        <v>581987</v>
       </c>
       <c r="R26" t="n">
-        <v>7194433</v>
+        <v>7193934</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3503,7 +3492,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3513,7 +3502,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3540,10 +3529,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120922486</v>
+        <v>120922481</v>
       </c>
       <c r="B27" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3556,34 +3545,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582067</v>
+        <v>582249</v>
       </c>
       <c r="R27" t="n">
-        <v>7194258</v>
+        <v>7194088</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3615,7 +3609,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3625,7 +3619,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3652,10 +3646,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120922482</v>
+        <v>120922586</v>
       </c>
       <c r="B28" t="n">
-        <v>57504</v>
+        <v>80558</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3668,38 +3662,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>1049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582136</v>
+        <v>582040</v>
       </c>
       <c r="R28" t="n">
-        <v>7194281</v>
+        <v>7193935</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3731,7 +3721,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3741,7 +3731,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3768,10 +3758,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120922586</v>
+        <v>120922485</v>
       </c>
       <c r="B29" t="n">
-        <v>80558</v>
+        <v>79718</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3780,25 +3770,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1049</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3808,10 +3798,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>582040</v>
+        <v>582071</v>
       </c>
       <c r="R29" t="n">
-        <v>7193935</v>
+        <v>7194257</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3843,7 +3833,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3853,7 +3843,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3880,10 +3870,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120922484</v>
+        <v>120922591</v>
       </c>
       <c r="B30" t="n">
-        <v>79642</v>
+        <v>78601</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3892,25 +3882,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3920,10 +3910,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>582070</v>
+        <v>582228</v>
       </c>
       <c r="R30" t="n">
-        <v>7194257</v>
+        <v>7193932</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3955,7 +3945,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3965,7 +3955,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3992,10 +3982,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120922503</v>
+        <v>120922486</v>
       </c>
       <c r="B31" t="n">
-        <v>91090</v>
+        <v>78601</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4008,16 +3998,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4027,10 +4022,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581741</v>
+        <v>582067</v>
       </c>
       <c r="R31" t="n">
-        <v>7194429</v>
+        <v>7194258</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4062,7 +4057,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4072,7 +4067,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4099,10 +4094,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120922504</v>
+        <v>120922488</v>
       </c>
       <c r="B32" t="n">
-        <v>90697</v>
+        <v>57351</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4115,34 +4110,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581741</v>
+        <v>581950</v>
       </c>
       <c r="R32" t="n">
-        <v>7194431</v>
+        <v>7194247</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4211,10 +4211,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120922485</v>
+        <v>120922483</v>
       </c>
       <c r="B33" t="n">
-        <v>79718</v>
+        <v>79683</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4223,25 +4223,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4251,10 +4251,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>582071</v>
+        <v>582070</v>
       </c>
       <c r="R33" t="n">
-        <v>7194257</v>
+        <v>7194255</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4323,10 +4323,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120922512</v>
+        <v>120922502</v>
       </c>
       <c r="B34" t="n">
-        <v>78601</v>
+        <v>90983</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4339,21 +4339,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4363,10 +4363,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581763</v>
+        <v>581743</v>
       </c>
       <c r="R34" t="n">
-        <v>7194521</v>
+        <v>7194428</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4435,10 +4435,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120922587</v>
+        <v>120922588</v>
       </c>
       <c r="B35" t="n">
-        <v>77985</v>
+        <v>78601</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4451,21 +4451,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4547,7 +4547,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120922588</v>
+        <v>120922590</v>
       </c>
       <c r="B36" t="n">
         <v>78601</v>
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>582037</v>
+        <v>582118</v>
       </c>
       <c r="R36" t="n">
-        <v>7193934</v>
+        <v>7193927</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4659,10 +4659,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120922488</v>
+        <v>120922504</v>
       </c>
       <c r="B37" t="n">
-        <v>57351</v>
+        <v>90697</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4675,39 +4675,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581950</v>
+        <v>581741</v>
       </c>
       <c r="R37" t="n">
-        <v>7194247</v>
+        <v>7194431</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4739,7 +4734,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4749,7 +4744,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4776,10 +4771,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120922501</v>
+        <v>120922484</v>
       </c>
       <c r="B38" t="n">
-        <v>91041</v>
+        <v>79642</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4788,25 +4783,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2062</v>
+        <v>229497</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4816,10 +4811,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581743</v>
+        <v>582070</v>
       </c>
       <c r="R38" t="n">
-        <v>7194427</v>
+        <v>7194257</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4851,7 +4846,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4861,7 +4856,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4872,21 +4867,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4903,10 +4883,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120922502</v>
+        <v>120922512</v>
       </c>
       <c r="B39" t="n">
-        <v>90983</v>
+        <v>78601</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4919,21 +4899,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4943,10 +4923,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581743</v>
+        <v>581763</v>
       </c>
       <c r="R39" t="n">
-        <v>7194428</v>
+        <v>7194521</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4978,7 +4958,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4988,7 +4968,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5015,7 +4995,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120922515</v>
+        <v>120922589</v>
       </c>
       <c r="B40" t="n">
         <v>78601</v>
@@ -5055,10 +5035,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>581662</v>
+        <v>582049</v>
       </c>
       <c r="R40" t="n">
-        <v>7194722</v>
+        <v>7193913</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5090,7 +5070,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5100,7 +5080,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5127,10 +5107,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120922489</v>
+        <v>120922587</v>
       </c>
       <c r="B41" t="n">
-        <v>78601</v>
+        <v>77985</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5143,21 +5123,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5167,10 +5147,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581929</v>
+        <v>582037</v>
       </c>
       <c r="R41" t="n">
-        <v>7194255</v>
+        <v>7193934</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5202,7 +5182,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5212,7 +5192,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5239,10 +5219,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120922483</v>
+        <v>120922513</v>
       </c>
       <c r="B42" t="n">
-        <v>79683</v>
+        <v>74708</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5255,21 +5235,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5279,10 +5259,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>582070</v>
+        <v>581664</v>
       </c>
       <c r="R42" t="n">
-        <v>7194255</v>
+        <v>7194719</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5314,7 +5294,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5324,7 +5304,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5351,7 +5331,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120922508</v>
+        <v>120922489</v>
       </c>
       <c r="B43" t="n">
         <v>78601</v>
@@ -5391,10 +5371,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581736</v>
+        <v>581929</v>
       </c>
       <c r="R43" t="n">
-        <v>7194434</v>
+        <v>7194255</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5426,7 +5406,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5436,7 +5416,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5463,10 +5443,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120922500</v>
+        <v>120922515</v>
       </c>
       <c r="B44" t="n">
-        <v>90693</v>
+        <v>78601</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5479,21 +5459,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5503,10 +5483,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581739</v>
+        <v>581662</v>
       </c>
       <c r="R44" t="n">
-        <v>7194428</v>
+        <v>7194722</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5538,7 +5518,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5548,7 +5528,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5575,10 +5555,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120922591</v>
+        <v>120922584</v>
       </c>
       <c r="B45" t="n">
-        <v>78601</v>
+        <v>79683</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5591,21 +5571,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5615,10 +5595,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>582228</v>
+        <v>581988</v>
       </c>
       <c r="R45" t="n">
-        <v>7193932</v>
+        <v>7193931</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5650,7 +5630,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5660,7 +5640,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5687,10 +5667,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120922584</v>
+        <v>120922501</v>
       </c>
       <c r="B46" t="n">
-        <v>79683</v>
+        <v>91041</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5699,25 +5679,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>2062</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5727,10 +5707,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581988</v>
+        <v>581743</v>
       </c>
       <c r="R46" t="n">
-        <v>7193931</v>
+        <v>7194427</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5762,7 +5742,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5772,7 +5752,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5783,6 +5763,21 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5911,10 +5906,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120922589</v>
+        <v>120922487</v>
       </c>
       <c r="B48" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5927,34 +5922,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>582049</v>
+        <v>582033</v>
       </c>
       <c r="R48" t="n">
-        <v>7193913</v>
+        <v>7194312</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5986,7 +5986,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 42064-2024 artfynd.xlsx
+++ b/artfynd/A 42064-2024 artfynd.xlsx
@@ -3189,10 +3189,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120922500</v>
+        <v>120922482</v>
       </c>
       <c r="B24" t="n">
-        <v>90693</v>
+        <v>57504</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3205,34 +3205,38 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581739</v>
+        <v>582136</v>
       </c>
       <c r="R24" t="n">
-        <v>7194428</v>
+        <v>7194281</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3264,7 +3268,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3274,7 +3278,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3301,10 +3305,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120922482</v>
+        <v>120922500</v>
       </c>
       <c r="B25" t="n">
-        <v>57504</v>
+        <v>90693</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3317,38 +3321,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582136</v>
+        <v>581739</v>
       </c>
       <c r="R25" t="n">
-        <v>7194281</v>
+        <v>7194428</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4659,10 +4659,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120922504</v>
+        <v>120922484</v>
       </c>
       <c r="B37" t="n">
-        <v>90697</v>
+        <v>79642</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4671,25 +4671,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4699,10 +4699,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581741</v>
+        <v>582070</v>
       </c>
       <c r="R37" t="n">
-        <v>7194431</v>
+        <v>7194257</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4771,10 +4771,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120922484</v>
+        <v>120922504</v>
       </c>
       <c r="B38" t="n">
-        <v>79642</v>
+        <v>90697</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4783,25 +4783,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4811,10 +4811,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>582070</v>
+        <v>581741</v>
       </c>
       <c r="R38" t="n">
-        <v>7194257</v>
+        <v>7194431</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 42064-2024 artfynd.xlsx
+++ b/artfynd/A 42064-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115417711</v>
+        <v>120922502</v>
       </c>
       <c r="B2" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582076</v>
+        <v>581743</v>
       </c>
       <c r="R2" t="n">
-        <v>7194264</v>
+        <v>7194428</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115413251</v>
+        <v>120922576</v>
       </c>
       <c r="B3" t="n">
-        <v>74647</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582099</v>
+        <v>581964</v>
       </c>
       <c r="R3" t="n">
-        <v>7194257</v>
+        <v>7193918</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -857,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115413303</v>
+        <v>120922586</v>
       </c>
       <c r="B4" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,43 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581907</v>
+        <v>582040</v>
       </c>
       <c r="R4" t="n">
-        <v>7194463</v>
+        <v>7193935</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,22 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,15 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115417787</v>
+        <v>120922500</v>
       </c>
       <c r="B5" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581779</v>
+        <v>581739</v>
       </c>
       <c r="R5" t="n">
-        <v>7194538</v>
+        <v>7194428</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1090,22 +1061,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,15 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115417799</v>
+        <v>120922507</v>
       </c>
       <c r="B6" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1172,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582227</v>
+        <v>581739</v>
       </c>
       <c r="R6" t="n">
-        <v>7194092</v>
+        <v>7194433</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1202,22 +1168,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,15 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115417792</v>
+        <v>120922504</v>
       </c>
       <c r="B7" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1284,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582061</v>
+        <v>581741</v>
       </c>
       <c r="R7" t="n">
-        <v>7194269</v>
+        <v>7194431</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1314,22 +1275,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,15 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115417797</v>
+        <v>120922577</v>
       </c>
       <c r="B8" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1396,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582180</v>
+        <v>581965</v>
       </c>
       <c r="R8" t="n">
-        <v>7194186</v>
+        <v>7193917</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1426,22 +1382,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,15 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115417793</v>
+        <v>115417805</v>
       </c>
       <c r="B9" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582076</v>
+        <v>582227</v>
       </c>
       <c r="R9" t="n">
-        <v>7194264</v>
+        <v>7194091</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1543,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1553,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1580,15 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115417790</v>
+        <v>120922578</v>
       </c>
       <c r="B10" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1620,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581840</v>
+        <v>581966</v>
       </c>
       <c r="R10" t="n">
-        <v>7194503</v>
+        <v>7193919</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1650,22 +1596,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,15 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115413305</v>
+        <v>120922580</v>
       </c>
       <c r="B11" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,43 +1649,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582237</v>
+        <v>581971</v>
       </c>
       <c r="R11" t="n">
-        <v>7194070</v>
+        <v>7193909</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1771,22 +1703,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,37 +1745,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115417802</v>
+        <v>120922501</v>
       </c>
       <c r="B12" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92281</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1853,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582231</v>
+        <v>581743</v>
       </c>
       <c r="R12" t="n">
-        <v>7194065</v>
+        <v>7194428</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1883,22 +1810,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1909,6 +1836,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1925,15 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115413292</v>
+        <v>115417672</v>
       </c>
       <c r="B13" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1941,39 +1878,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582235</v>
+        <v>582059</v>
       </c>
       <c r="R13" t="n">
-        <v>7194066</v>
+        <v>7194265</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2005,7 +1937,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2015,7 +1947,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2042,15 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115417699</v>
+        <v>120922483</v>
       </c>
       <c r="B14" t="n">
-        <v>56470</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2058,43 +1985,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582177</v>
+        <v>582070</v>
       </c>
       <c r="R14" t="n">
-        <v>7194188</v>
+        <v>7194255</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2121,22 +2039,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2163,15 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115417674</v>
+        <v>120922584</v>
       </c>
       <c r="B15" t="n">
-        <v>55873</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2179,43 +2092,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>206004</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581892</v>
+        <v>581988</v>
       </c>
       <c r="R15" t="n">
-        <v>7194495</v>
+        <v>7193931</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2242,22 +2146,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2284,37 +2188,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115417684</v>
+        <v>115417787</v>
       </c>
       <c r="B16" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2324,10 +2223,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582060</v>
+        <v>581779</v>
       </c>
       <c r="R16" t="n">
-        <v>7194265</v>
+        <v>7194538</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2359,7 +2258,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2369,7 +2268,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2396,19 +2295,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115417795</v>
+        <v>115417790</v>
       </c>
       <c r="B17" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2436,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582103</v>
+        <v>581840</v>
       </c>
       <c r="R17" t="n">
-        <v>7194259</v>
+        <v>7194503</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2471,7 +2365,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2481,7 +2375,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2508,37 +2402,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115417672</v>
+        <v>115417792</v>
       </c>
       <c r="B18" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2548,10 +2437,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582059</v>
+        <v>582061</v>
       </c>
       <c r="R18" t="n">
-        <v>7194265</v>
+        <v>7194269</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2620,37 +2509,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115417805</v>
+        <v>115417793</v>
       </c>
       <c r="B19" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2660,10 +2544,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582227</v>
+        <v>582076</v>
       </c>
       <c r="R19" t="n">
-        <v>7194091</v>
+        <v>7194264</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2695,7 +2579,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2705,7 +2589,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2732,64 +2616,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115417698</v>
+        <v>115417795</v>
       </c>
       <c r="B20" t="n">
-        <v>56470</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Luspberget, Vojmsjön, Ås lm</t>
+          <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581956</v>
+        <v>582103</v>
       </c>
       <c r="R20" t="n">
-        <v>7194522</v>
+        <v>7194259</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2821,7 +2686,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2831,7 +2696,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2858,32 +2723,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120922503</v>
+        <v>115417797</v>
       </c>
       <c r="B21" t="n">
-        <v>91090</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2893,10 +2758,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581741</v>
+        <v>582180</v>
       </c>
       <c r="R21" t="n">
-        <v>7194429</v>
+        <v>7194186</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2923,22 +2788,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2965,37 +2830,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120922507</v>
+        <v>115417799</v>
       </c>
       <c r="B22" t="n">
-        <v>90693</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3005,10 +2865,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581739</v>
+        <v>582227</v>
       </c>
       <c r="R22" t="n">
-        <v>7194433</v>
+        <v>7194092</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3035,22 +2895,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3077,19 +2937,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120922508</v>
+        <v>115417802</v>
       </c>
       <c r="B23" t="n">
-        <v>78601</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3117,10 +2972,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581736</v>
+        <v>582231</v>
       </c>
       <c r="R23" t="n">
-        <v>7194434</v>
+        <v>7194065</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3147,22 +3002,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3189,54 +3044,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120922482</v>
+        <v>115417803</v>
       </c>
       <c r="B24" t="n">
-        <v>57504</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582136</v>
+        <v>582273</v>
       </c>
       <c r="R24" t="n">
-        <v>7194281</v>
+        <v>7194059</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3263,22 +3109,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3305,37 +3151,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120922500</v>
+        <v>120922486</v>
       </c>
       <c r="B25" t="n">
-        <v>90693</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3345,10 +3186,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581739</v>
+        <v>582067</v>
       </c>
       <c r="R25" t="n">
-        <v>7194428</v>
+        <v>7194258</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3380,7 +3221,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3390,7 +3231,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3417,19 +3258,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120922585</v>
+        <v>120922489</v>
       </c>
       <c r="B26" t="n">
-        <v>78601</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3457,10 +3293,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581987</v>
+        <v>581929</v>
       </c>
       <c r="R26" t="n">
-        <v>7193934</v>
+        <v>7194255</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3492,7 +3328,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3502,7 +3338,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3529,55 +3365,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120922481</v>
+        <v>120922508</v>
       </c>
       <c r="B27" t="n">
-        <v>57351</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582249</v>
+        <v>581736</v>
       </c>
       <c r="R27" t="n">
-        <v>7194088</v>
+        <v>7194434</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3609,7 +3435,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3619,7 +3445,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3646,37 +3472,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120922586</v>
+        <v>120922510</v>
       </c>
       <c r="B28" t="n">
-        <v>80558</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3686,10 +3507,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582040</v>
+        <v>581763</v>
       </c>
       <c r="R28" t="n">
-        <v>7193935</v>
+        <v>7194446</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3721,7 +3542,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3731,7 +3552,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3758,37 +3579,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120922485</v>
+        <v>120922512</v>
       </c>
       <c r="B29" t="n">
-        <v>79718</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3798,10 +3614,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>582071</v>
+        <v>581763</v>
       </c>
       <c r="R29" t="n">
-        <v>7194257</v>
+        <v>7194521</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3833,7 +3649,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3843,7 +3659,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3870,19 +3686,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120922591</v>
+        <v>120922515</v>
       </c>
       <c r="B30" t="n">
-        <v>78601</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3910,10 +3721,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>582228</v>
+        <v>581662</v>
       </c>
       <c r="R30" t="n">
-        <v>7193932</v>
+        <v>7194722</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3945,7 +3756,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3955,7 +3766,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3982,19 +3793,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120922486</v>
+        <v>120922516</v>
       </c>
       <c r="B31" t="n">
-        <v>78601</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -4022,10 +3828,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>582067</v>
+        <v>581511</v>
       </c>
       <c r="R31" t="n">
-        <v>7194258</v>
+        <v>7194758</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4057,7 +3863,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4067,7 +3873,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4094,55 +3900,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120922488</v>
+        <v>120922579</v>
       </c>
       <c r="B32" t="n">
-        <v>57351</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581950</v>
+        <v>581970</v>
       </c>
       <c r="R32" t="n">
-        <v>7194247</v>
+        <v>7193921</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4174,7 +3970,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4184,7 +3980,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4211,37 +4007,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120922483</v>
+        <v>120922581</v>
       </c>
       <c r="B33" t="n">
-        <v>79683</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4251,10 +4042,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>582070</v>
+        <v>581973</v>
       </c>
       <c r="R33" t="n">
-        <v>7194255</v>
+        <v>7193915</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4286,7 +4077,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4296,7 +4087,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4323,37 +4114,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120922502</v>
+        <v>120922583</v>
       </c>
       <c r="B34" t="n">
-        <v>90983</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4363,10 +4149,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581743</v>
+        <v>581974</v>
       </c>
       <c r="R34" t="n">
-        <v>7194428</v>
+        <v>7193913</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4398,7 +4184,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4408,7 +4194,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4435,19 +4221,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120922588</v>
+        <v>120922585</v>
       </c>
       <c r="B35" t="n">
-        <v>78601</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4475,7 +4256,7 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>582037</v>
+        <v>581987</v>
       </c>
       <c r="R35" t="n">
         <v>7193934</v>
@@ -4510,7 +4291,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4520,7 +4301,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4547,19 +4328,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120922590</v>
+        <v>120922588</v>
       </c>
       <c r="B36" t="n">
-        <v>78601</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4587,10 +4363,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>582118</v>
+        <v>582037</v>
       </c>
       <c r="R36" t="n">
-        <v>7193927</v>
+        <v>7193934</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4622,7 +4398,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4632,7 +4408,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4659,37 +4435,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120922484</v>
+        <v>120922589</v>
       </c>
       <c r="B37" t="n">
-        <v>79642</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4699,10 +4470,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>582070</v>
+        <v>582049</v>
       </c>
       <c r="R37" t="n">
-        <v>7194257</v>
+        <v>7193913</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4734,7 +4505,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4744,7 +4515,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4771,37 +4542,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120922504</v>
+        <v>120922590</v>
       </c>
       <c r="B38" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4811,10 +4577,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581741</v>
+        <v>582118</v>
       </c>
       <c r="R38" t="n">
-        <v>7194431</v>
+        <v>7193927</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4846,7 +4612,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4856,7 +4622,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4883,19 +4649,14 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120922512</v>
+        <v>120922591</v>
       </c>
       <c r="B39" t="n">
-        <v>78601</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4923,10 +4684,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581763</v>
+        <v>582228</v>
       </c>
       <c r="R39" t="n">
-        <v>7194521</v>
+        <v>7193932</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4958,7 +4719,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4968,7 +4729,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4995,19 +4756,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120922589</v>
+        <v>120922592</v>
       </c>
       <c r="B40" t="n">
-        <v>78601</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -5035,10 +4791,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>582049</v>
+        <v>582324</v>
       </c>
       <c r="R40" t="n">
-        <v>7193913</v>
+        <v>7193983</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5070,7 +4826,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5080,7 +4836,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5110,12 +4866,7 @@
         <v>120922587</v>
       </c>
       <c r="B41" t="n">
-        <v>77985</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5219,15 +4970,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120922513</v>
+        <v>115413251</v>
       </c>
       <c r="B42" t="n">
-        <v>74708</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5259,10 +5005,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581664</v>
+        <v>582099</v>
       </c>
       <c r="R42" t="n">
-        <v>7194719</v>
+        <v>7194257</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5289,22 +5035,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5331,15 +5077,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120922489</v>
+        <v>120922513</v>
       </c>
       <c r="B43" t="n">
-        <v>78601</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5347,21 +5088,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5371,10 +5112,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581929</v>
+        <v>581664</v>
       </c>
       <c r="R43" t="n">
-        <v>7194255</v>
+        <v>7194719</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5406,7 +5147,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5416,7 +5157,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5443,37 +5184,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120922515</v>
+        <v>115417684</v>
       </c>
       <c r="B44" t="n">
-        <v>78601</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5483,10 +5219,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581662</v>
+        <v>582060</v>
       </c>
       <c r="R44" t="n">
-        <v>7194722</v>
+        <v>7194265</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5513,22 +5249,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5555,37 +5291,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120922584</v>
+        <v>120922485</v>
       </c>
       <c r="B45" t="n">
-        <v>79683</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5595,10 +5326,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581988</v>
+        <v>582071</v>
       </c>
       <c r="R45" t="n">
-        <v>7193931</v>
+        <v>7194257</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5630,7 +5361,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5640,7 +5371,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5667,37 +5398,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120922501</v>
+        <v>120922582</v>
       </c>
       <c r="B46" t="n">
-        <v>91041</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2062</v>
+        <v>6464</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5707,10 +5433,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581743</v>
+        <v>581974</v>
       </c>
       <c r="R46" t="n">
-        <v>7194427</v>
+        <v>7193911</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5742,7 +5468,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5752,7 +5478,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5763,21 +5489,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5794,15 +5505,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120922510</v>
+        <v>115413292</v>
       </c>
       <c r="B47" t="n">
-        <v>78601</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5810,34 +5516,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581763</v>
+        <v>582235</v>
       </c>
       <c r="R47" t="n">
-        <v>7194446</v>
+        <v>7194066</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5864,22 +5575,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5906,15 +5617,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120922487</v>
+        <v>120922481</v>
       </c>
       <c r="B48" t="n">
-        <v>57351</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5951,10 +5657,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>582033</v>
+        <v>582249</v>
       </c>
       <c r="R48" t="n">
-        <v>7194312</v>
+        <v>7194088</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5986,7 +5692,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5996,7 +5702,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6020,6 +5726,1140 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>120922487</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Luspberget, Vojmsjödammen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>582033</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7194312</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>120922488</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Luspberget, Vojmsjödammen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>581950</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7194247</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>115417698</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Luspberget, Vojmsjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>581956</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7194522</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>115417699</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Luspberget, Vojmsjödammen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>582177</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7194188</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>115413303</v>
+      </c>
+      <c r="B53" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Luspberget, Vojmsjödammen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>581907</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7194463</v>
+      </c>
+      <c r="S53" t="n">
+        <v>25</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>115413305</v>
+      </c>
+      <c r="B54" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Luspberget, Vojmsjödammen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>582237</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7194070</v>
+      </c>
+      <c r="S54" t="n">
+        <v>25</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>08:36</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>08:36</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>120922482</v>
+      </c>
+      <c r="B55" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Luspberget, Vojmsjödammen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>582136</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7194281</v>
+      </c>
+      <c r="S55" t="n">
+        <v>25</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>115417674</v>
+      </c>
+      <c r="B56" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Luspberget, Vojmsjödammen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>581892</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7194495</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>120922484</v>
+      </c>
+      <c r="B57" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Luspberget, Vojmsjödammen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>582070</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7194257</v>
+      </c>
+      <c r="S57" t="n">
+        <v>25</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>120922503</v>
+      </c>
+      <c r="B58" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Luspberget, Vojmsjödammen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>581741</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7194429</v>
+      </c>
+      <c r="S58" t="n">
+        <v>25</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
